--- a/assets/fcf/Financial Statements & Free Cash Flow Review.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow Review.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flows\4 - Exercises\1 - Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB28C87-0C7C-44C0-97AC-DBDC787E8ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA9094B-B879-4591-A7A4-A3EDFF59E6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Description" sheetId="9" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="61">
   <si>
     <t>Cash</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>Sales is projected to be $2000 with a gross profit margin of 20% (i.e. $1,600 in COGS) in years 1 through 5.</t>
+  </si>
+  <si>
+    <t>=EBIT</t>
   </si>
 </sst>
 </file>
@@ -357,7 +360,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -424,28 +427,31 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -879,10 +885,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="51"/>
+      <c r="B1" s="46"/>
       <c r="C1" s="15" t="s">
         <v>24</v>
       </c>
@@ -900,10 +906,10 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="52"/>
+      <c r="B2" s="47"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -936,10 +942,10 @@
       <c r="J4" s="11"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="53"/>
+      <c r="A5" s="54" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="50"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
@@ -983,10 +989,10 @@
       <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A9" s="50" t="s">
+      <c r="A9" s="53" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="50"/>
+      <c r="B9" s="53"/>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
       <c r="E9" s="27"/>
@@ -994,10 +1000,10 @@
       <c r="G9" s="27"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A10" s="46" t="s">
+      <c r="A10" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="46"/>
+      <c r="B10" s="51"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
@@ -1007,10 +1013,10 @@
       <c r="I10" s="20"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A11" s="46" t="s">
+      <c r="A11" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="46"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
@@ -1021,23 +1027,23 @@
       <c r="K11" s="22"/>
     </row>
     <row r="14" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
+      <c r="J14" s="52"/>
+      <c r="K14" s="52"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
     </row>
     <row r="15" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A15" s="2" t="s">
@@ -1468,11 +1474,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A14:O14"/>
     <mergeCell ref="A7:B7"/>
@@ -1480,6 +1481,11 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/assets/fcf/Financial Statements & Free Cash Flow Review.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow Review.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\4 - Exercises\1 - Review\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics Spring 2025\Course\3 - Financial Statements &amp; Free Cash Flow\4 - Exercises\1 - Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA9094B-B879-4591-A7A4-A3EDFF59E6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2527DD99-12E4-4108-B38D-98FE2C0D99FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Description" sheetId="9" r:id="rId1"/>
@@ -165,9 +165,6 @@
     <t>Balance Sheet</t>
   </si>
   <si>
-    <t>You will raise capital will come from three sources:</t>
-  </si>
-  <si>
     <t>The corporate tax rate is 30%.</t>
   </si>
   <si>
@@ -220,6 +217,9 @@
   </si>
   <si>
     <t>=EBIT</t>
+  </si>
+  <si>
+    <t>You will raise capital from three sources:</t>
   </si>
 </sst>
 </file>
@@ -427,31 +427,31 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -791,81 +791,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDAEB0D-3A27-486D-AC6C-E43C29FCDDD3}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -876,19 +876,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551FB90-26B1-44C9-90FF-AB3D820DD8A7}">
   <dimension ref="A1:O52"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="8.59765625" style="12" customWidth="1"/>
-    <col min="9" max="9" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="8.59765625" customWidth="1"/>
+    <col min="1" max="1" width="29.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="8.6328125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="15" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="46"/>
+      <c r="B1" s="51"/>
       <c r="C1" s="15" t="s">
         <v>24</v>
       </c>
@@ -899,17 +899,17 @@
         <v>26</v>
       </c>
       <c r="F1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A2" s="47" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="47"/>
+      <c r="B2" s="52"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -917,7 +917,7 @@
       <c r="G2" s="25"/>
       <c r="J2" s="11"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="48" t="s">
         <v>27</v>
       </c>
@@ -929,7 +929,7 @@
       <c r="G3" s="25"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="49" t="s">
         <v>17</v>
       </c>
@@ -941,11 +941,11 @@
       <c r="G4" s="24"/>
       <c r="J4" s="11"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A5" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="50"/>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="54"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
@@ -953,7 +953,7 @@
       <c r="G5" s="25"/>
       <c r="L5" s="17"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="49" t="s">
         <v>19</v>
       </c>
@@ -965,7 +965,7 @@
       <c r="G6" s="26"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="48" t="s">
         <v>20</v>
       </c>
@@ -976,7 +976,7 @@
       <c r="F7" s="25"/>
       <c r="G7" s="25"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="49" t="s">
         <v>21</v>
       </c>
@@ -988,22 +988,22 @@
       <c r="G8" s="24"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A9" s="53" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="53"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="27"/>
       <c r="D9" s="27"/>
       <c r="E9" s="27"/>
       <c r="F9" s="27"/>
       <c r="G9" s="27"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A10" s="51" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="51"/>
+      <c r="B10" s="46"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
@@ -1012,11 +1012,11 @@
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A11" s="51" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="51"/>
+      <c r="B11" s="46"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
@@ -1026,26 +1026,26 @@
       <c r="I11" s="20"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="14" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="52" t="s">
+    <row r="14" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-      <c r="M14" s="52"/>
-      <c r="N14" s="52"/>
-      <c r="O14" s="52"/>
-    </row>
-    <row r="15" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+      <c r="M14" s="47"/>
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+    </row>
+    <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>10</v>
       </c>
@@ -1062,10 +1062,10 @@
         <v>26</v>
       </c>
       <c r="F15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="I15" s="9" t="s">
         <v>11</v>
@@ -1083,13 +1083,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="O15" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1110,7 @@
       <c r="N16" s="25"/>
       <c r="O16" s="25"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
@@ -1131,7 +1131,7 @@
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
         <v>2</v>
       </c>
@@ -1152,7 +1152,7 @@
       <c r="N18" s="24"/>
       <c r="O18" s="24"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1172,7 +1172,7 @@
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="12"/>
@@ -1180,7 +1180,7 @@
       <c r="N20" s="12"/>
       <c r="O20" s="12"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="I21" s="7" t="s">
         <v>8</v>
       </c>
@@ -1191,7 +1191,7 @@
       <c r="N21" s="32"/>
       <c r="O21" s="32"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="I22" s="3" t="s">
         <v>9</v>
       </c>
@@ -1202,7 +1202,7 @@
       <c r="N22" s="33"/>
       <c r="O22" s="33"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1222,7 +1222,7 @@
       <c r="N24" s="25"/>
       <c r="O24" s="25"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>40</v>
       </c>
@@ -1242,7 +1242,7 @@
       <c r="N25" s="35"/>
       <c r="O25" s="35"/>
     </row>
-    <row r="26" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="8" t="s">
         <v>4</v>
       </c>
@@ -1262,7 +1262,7 @@
       <c r="N26" s="36"/>
       <c r="O26" s="36"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="J28" s="12"/>
       <c r="K28" s="12"/>
       <c r="L28" s="12"/>
@@ -1270,7 +1270,7 @@
       <c r="N28" s="12"/>
       <c r="O28" s="12"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
         <v>5</v>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="N29" s="38"/>
       <c r="O29" s="38"/>
     </row>
-    <row r="31" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B31" s="15" t="s">
         <v>23</v>
       </c>
@@ -1304,13 +1304,13 @@
         <v>26</v>
       </c>
       <c r="F31" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G31" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.45">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>30</v>
       </c>
@@ -1341,7 +1341,7 @@
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
     </row>
-    <row r="35" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
@@ -1358,13 +1358,13 @@
         <v>26</v>
       </c>
       <c r="F35" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G35" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G35" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>18</v>
       </c>
@@ -1376,7 +1376,7 @@
       <c r="G36" s="28"/>
       <c r="H36" s="13"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -1387,7 +1387,7 @@
       <c r="F37" s="31"/>
       <c r="G37" s="31"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>33</v>
       </c>
@@ -1398,7 +1398,7 @@
       <c r="F38" s="39"/>
       <c r="G38" s="39"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>34</v>
       </c>
@@ -1409,7 +1409,7 @@
       <c r="F39" s="40"/>
       <c r="G39" s="40"/>
     </row>
-    <row r="40" spans="1:8" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
         <v>35</v>
       </c>
@@ -1420,7 +1420,7 @@
       <c r="F40" s="42"/>
       <c r="G40" s="42"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
         <v>32</v>
       </c>
@@ -1431,12 +1431,12 @@
       <c r="F41" s="37"/>
       <c r="G41" s="37"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="H42" s="44"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="38"/>
       <c r="C43" s="44"/>
@@ -1446,7 +1446,7 @@
       <c r="G43" s="44"/>
       <c r="H43" s="43"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="21"/>
       <c r="B44" s="45"/>
       <c r="C44" s="43"/>
@@ -1455,7 +1455,7 @@
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
     </row>
-    <row r="51" spans="9:15" x14ac:dyDescent="0.45">
+    <row r="51" spans="9:15" x14ac:dyDescent="0.35">
       <c r="J51" s="12"/>
       <c r="K51" s="12"/>
       <c r="L51" s="12"/>
@@ -1463,7 +1463,7 @@
       <c r="N51" s="12"/>
       <c r="O51" s="12"/>
     </row>
-    <row r="52" spans="9:15" x14ac:dyDescent="0.45">
+    <row r="52" spans="9:15" x14ac:dyDescent="0.35">
       <c r="I52" s="5"/>
       <c r="J52" s="14"/>
       <c r="K52" s="14"/>
@@ -1474,6 +1474,11 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A14:O14"/>
     <mergeCell ref="A7:B7"/>
@@ -1481,11 +1486,6 @@
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
